--- a/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_3_kato_katz.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_3_kato_katz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154A4894-C17C-423D-B279-1F2843461C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A04FB3-6616-4EAB-A9BA-0419E544DB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="100">
   <si>
     <t>type</t>
   </si>
@@ -261,9 +261,6 @@
     <t>not(selected(${C3}, ${k_code_id})) and regex(., '^\d{2}_\d{3}_\d{1,3}$')</t>
   </si>
   <si>
-    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte</t>
-  </si>
-  <si>
     <t>Schistosoma mansoni (oeufs) - lame A</t>
   </si>
   <si>
@@ -319,6 +316,12 @@
   </si>
   <si>
     <t>k_eggs_other_parasite_sb</t>
+  </si>
+  <si>
+    <t>exemple: 12_123_1</t>
+  </si>
+  <si>
+    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte. Exemple d'un code 34_567_890</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1248,7 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="1:17" s="41" customFormat="1" ht="47.25">
+    <row r="11" spans="1:17" s="41" customFormat="1" ht="63">
       <c r="A11" s="28" t="s">
         <v>18</v>
       </c>
@@ -1255,13 +1258,15 @@
       <c r="C11" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="40"/>
+      <c r="D11" s="40" t="s">
+        <v>98</v>
+      </c>
       <c r="E11" s="33"/>
       <c r="F11" s="26" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
@@ -1313,7 +1318,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="42"/>
@@ -1332,10 +1337,10 @@
         <v>19</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="42"/>
@@ -1357,7 +1362,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="42"/>
@@ -1380,10 +1385,10 @@
         <v>19</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="42"/>
@@ -1409,7 +1414,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="42"/>
@@ -1432,10 +1437,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="42"/>
@@ -1461,7 +1466,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D19" s="44"/>
       <c r="E19" s="42"/>
@@ -1480,10 +1485,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="42"/>
@@ -1505,7 +1510,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" s="44"/>
       <c r="E21" s="42"/>
@@ -1520,10 +1525,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D22" s="44"/>
       <c r="E22" s="42"/>
@@ -1556,10 +1561,10 @@
         <v>19</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" s="44"/>
       <c r="E24" s="42"/>
@@ -1574,10 +1579,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25" s="44"/>
       <c r="E25" s="42"/>

--- a/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_3_kato_katz.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_3_kato_katz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A04FB3-6616-4EAB-A9BA-0419E544DB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF32F62-F6A7-4F7F-BBE8-8F05B59B7EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="103">
   <si>
     <t>type</t>
   </si>
@@ -231,36 +231,15 @@
     <t>end repeat</t>
   </si>
   <si>
-    <t>ml_sch_sth_impact_2501_3_kato_katz_v2</t>
-  </si>
-  <si>
-    <t>(2025 Jan) - 3. SCH/STH - Kato Katz V2</t>
-  </si>
-  <si>
     <t>Sélectionner l'aire de santé</t>
   </si>
   <si>
     <t>ml_ia_k_25012</t>
   </si>
   <si>
-    <t>k_code_id2</t>
-  </si>
-  <si>
     <t>Veuillez enregistrer le code unique de l’enfant et des échantillons de labo </t>
   </si>
   <si>
-    <t>Veuillez repéter le code unique</t>
-  </si>
-  <si>
-    <t>Le code répéter doit être le même</t>
-  </si>
-  <si>
-    <t>. = ${k_code_id}</t>
-  </si>
-  <si>
-    <t>not(selected(${C3}, ${k_code_id})) and regex(., '^\d{2}_\d{3}_\d{1,3}$')</t>
-  </si>
-  <si>
     <t>Schistosoma mansoni (oeufs) - lame A</t>
   </si>
   <si>
@@ -321,14 +300,44 @@
     <t>exemple: 12_123_1</t>
   </si>
   <si>
-    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte. Exemple d'un code 34_567_890</t>
+    <t>ml_sch_sth_impact_2501_3_kato_katz_v3</t>
+  </si>
+  <si>
+    <t>(2025 Jan) - 3. SCH/STH - Kato Katz V3</t>
+  </si>
+  <si>
+    <t>Veuillez entrer le code séquentiel</t>
+  </si>
+  <si>
+    <t>Répétez le code séquentiel</t>
+  </si>
+  <si>
+    <t>Le code répété doit être le même</t>
+  </si>
+  <si>
+    <t>k_sequential_code</t>
+  </si>
+  <si>
+    <t>k_sequential_code2</t>
+  </si>
+  <si>
+    <t>. = ${k_sequential_code}</t>
+  </si>
+  <si>
+    <t>concat(${k_site_id} , '_',  ${k_sequential_code})</t>
+  </si>
+  <si>
+    <t>not(selected(${C3}, ${k_code_id}))</t>
+  </si>
+  <si>
+    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte. Exemple d'un code 567_890</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -421,6 +430,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -539,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -663,6 +678,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="19.625" style="47" customWidth="1"/>
@@ -953,7 +989,7 @@
     <col min="3" max="3" width="47.5" style="47" customWidth="1"/>
     <col min="4" max="4" width="47.375" style="16" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="47" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="47" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="16" customWidth="1"/>
     <col min="8" max="8" width="22" style="16" customWidth="1"/>
     <col min="9" max="9" width="19.625" style="16" customWidth="1"/>
@@ -966,7 +1002,7 @@
     <col min="18" max="16384" width="11" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="9" customFormat="1" ht="18.75">
+    <row r="1" spans="1:19" s="9" customFormat="1" ht="18.75">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="9" customFormat="1">
+    <row r="2" spans="1:19" s="9" customFormat="1">
       <c r="A2" s="28" t="s">
         <v>19</v>
       </c>
@@ -1045,7 +1081,7 @@
       <c r="P2" s="30"/>
       <c r="Q2" s="30"/>
     </row>
-    <row r="3" spans="1:17" s="35" customFormat="1">
+    <row r="3" spans="1:19" s="35" customFormat="1">
       <c r="A3" s="28" t="s">
         <v>46</v>
       </c>
@@ -1073,7 +1109,7 @@
       <c r="P3" s="30"/>
       <c r="Q3" s="30"/>
     </row>
-    <row r="4" spans="1:17" s="35" customFormat="1">
+    <row r="4" spans="1:19" s="35" customFormat="1">
       <c r="A4" s="28" t="s">
         <v>46</v>
       </c>
@@ -1081,7 +1117,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="33"/>
@@ -1103,7 +1139,7 @@
       <c r="P4" s="30"/>
       <c r="Q4" s="30"/>
     </row>
-    <row r="5" spans="1:17" s="35" customFormat="1">
+    <row r="5" spans="1:19" s="35" customFormat="1">
       <c r="A5" s="28" t="s">
         <v>46</v>
       </c>
@@ -1133,7 +1169,7 @@
       </c>
       <c r="Q5" s="30"/>
     </row>
-    <row r="6" spans="1:17" s="38" customFormat="1">
+    <row r="6" spans="1:19" s="38" customFormat="1">
       <c r="A6" s="28" t="s">
         <v>46</v>
       </c>
@@ -1163,7 +1199,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1">
+    <row r="7" spans="1:19" s="9" customFormat="1">
       <c r="A7" s="19" t="s">
         <v>59</v>
       </c>
@@ -1184,12 +1220,12 @@
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
     </row>
-    <row r="8" spans="1:17" s="9" customFormat="1">
+    <row r="8" spans="1:19" s="9" customFormat="1">
       <c r="A8" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>62</v>
@@ -1206,7 +1242,7 @@
       <c r="M8" s="21"/>
       <c r="N8" s="18"/>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1">
+    <row r="9" spans="1:19" s="9" customFormat="1">
       <c r="A9" s="19" t="s">
         <v>59</v>
       </c>
@@ -1227,7 +1263,7 @@
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
-    <row r="10" spans="1:17" s="9" customFormat="1">
+    <row r="10" spans="1:19" s="9" customFormat="1">
       <c r="A10" s="19" t="s">
         <v>59</v>
       </c>
@@ -1248,99 +1284,114 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="1:17" s="41" customFormat="1" ht="63">
-      <c r="A11" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33" t="s">
+    <row r="11" spans="1:19" s="54" customFormat="1">
+      <c r="A11" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="51"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="53"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
-    </row>
-    <row r="12" spans="1:17" s="41" customFormat="1">
-      <c r="A12" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33" t="s">
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+    </row>
+    <row r="12" spans="1:19" s="54" customFormat="1" ht="31.5">
+      <c r="A12" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="49"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="53"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
-    </row>
-    <row r="13" spans="1:17" s="9" customFormat="1">
-      <c r="A13" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="12" t="s">
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+    </row>
+    <row r="13" spans="1:19" s="41" customFormat="1" ht="63">
+      <c r="A13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="33"/>
+      <c r="F13" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-    </row>
-    <row r="14" spans="1:17" s="9" customFormat="1">
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+    </row>
+    <row r="14" spans="1:19" s="9" customFormat="1">
       <c r="A14" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="42"/>
@@ -1354,15 +1405,15 @@
       <c r="K14" s="42"/>
       <c r="L14" s="42"/>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1">
+    <row r="15" spans="1:19" s="9" customFormat="1">
       <c r="A15" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="42"/>
@@ -1375,20 +1426,16 @@
       </c>
       <c r="K15" s="42"/>
       <c r="L15" s="42"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-    </row>
-    <row r="16" spans="1:17" s="9" customFormat="1">
+    </row>
+    <row r="16" spans="1:19" s="9" customFormat="1">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="42"/>
@@ -1411,10 +1458,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="42"/>
@@ -1428,19 +1475,19 @@
       <c r="K17" s="42"/>
       <c r="L17" s="42"/>
       <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
     </row>
     <row r="18" spans="1:17" s="9" customFormat="1">
       <c r="A18" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="42"/>
@@ -1462,13 +1509,13 @@
       <c r="A19" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" s="44"/>
+      <c r="B19" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="10"/>
       <c r="E19" s="42"/>
       <c r="F19" s="12"/>
       <c r="G19" s="43"/>
@@ -1479,16 +1526,20 @@
       </c>
       <c r="K19" s="42"/>
       <c r="L19" s="42"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
     </row>
     <row r="20" spans="1:17" s="9" customFormat="1">
       <c r="A20" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="42"/>
@@ -1507,10 +1558,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D21" s="44"/>
       <c r="E21" s="42"/>
@@ -1518,17 +1569,21 @@
       <c r="G21" s="43"/>
       <c r="H21" s="42"/>
       <c r="I21" s="42"/>
-      <c r="J21" s="12"/>
+      <c r="J21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
     </row>
     <row r="22" spans="1:17" s="9" customFormat="1">
       <c r="A22" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D22" s="44"/>
       <c r="E22" s="42"/>
@@ -1540,13 +1595,13 @@
     </row>
     <row r="23" spans="1:17" s="9" customFormat="1">
       <c r="A23" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="D23" s="44"/>
       <c r="E23" s="42"/>
@@ -1556,15 +1611,15 @@
       <c r="I23" s="42"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="1:17" s="9" customFormat="1" ht="31.5">
+    <row r="24" spans="1:17" s="9" customFormat="1">
       <c r="A24" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>94</v>
+        <v>44</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="D24" s="44"/>
       <c r="E24" s="42"/>
@@ -1579,10 +1634,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D25" s="44"/>
       <c r="E25" s="42"/>
@@ -1592,71 +1647,71 @@
       <c r="I25" s="42"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" s="9" customFormat="1" ht="31.5">
       <c r="A26" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="44"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="12"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B27" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="46" t="s">
+      <c r="D27" s="44"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="12" t="s">
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B29" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>30</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="44"/>
@@ -1669,17 +1724,35 @@
       <c r="K29" s="45"/>
       <c r="L29" s="45"/>
     </row>
-    <row r="33" spans="14:17">
-      <c r="N33" s="48"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-    </row>
-    <row r="39" spans="14:17">
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
+    <row r="30" spans="1:17">
+      <c r="A30" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+    </row>
+    <row r="34" spans="14:17">
+      <c r="N34" s="48"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+    </row>
+    <row r="40" spans="14:17">
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1767,10 +1840,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>38</v>
